--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117468865</v>
       </c>
       <c r="B2" t="n">
-        <v>57924</v>
+        <v>57925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125022524</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vapelbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>620128</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6913147</v>
+      </c>
+      <c r="S3" t="n">
+        <v>92</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125022524</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,134 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125650632</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57722</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vaple, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>620399</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6913078</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,11 +804,6 @@
       <c r="B3" t="n">
         <v>57914</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
@@ -926,12 +921,7 @@
         <v>125650632</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,6 +1038,130 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125714293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100108</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lundsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phylloscopus trochiloides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Sundevall, 1837)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vapelbäcken, Vaple, Njurunda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>620133</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6913154</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sjunger hela tiden!</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Lindström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Lindström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>125714293</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57956</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125650632</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>125714293</v>
       </c>
       <c r="B5" t="n">
-        <v>57956</v>
+        <v>57957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125650632</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>125714293</v>
       </c>
       <c r="B5" t="n">
-        <v>57957</v>
+        <v>57961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3002-2020 artfynd.xlsx
+++ b/artfynd/A 3002-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,6 +1163,133 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126487617</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57743</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vapelbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620128</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6913147</v>
+      </c>
+      <c r="S6" t="n">
+        <v>92</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sven Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
